--- a/assets/IT Support Tickets NGI.xlsx
+++ b/assets/IT Support Tickets NGI.xlsx
@@ -21,12 +21,15 @@
     <definedName name="SLA_Low">Configuration!$B$10</definedName>
     <definedName name="List_Categories">'Categories'!$A$2:$A$9</definedName>
     <definedName name="List_Engineers">'Users'!$A$2:$A$5</definedName>
-    <definedName name="List_Status">'Users'!$F$2:$F$6</definedName>
+    <definedName name="List_Status">'Users'!$F$2:$F$7</definedName>
     <definedName name="List_Priority">'Users'!$G$2:$G$4</definedName>
     <definedName name="List_Department">'Users'!$H$2:$H$9</definedName>
     <definedName name="List_Escalation">'Users'!$I$2:$I$5</definedName>
     <definedName name="List_Resolution">'Users'!$J$2:$J$10</definedName>
     <definedName name="List_ClosureReason">'Users'!$K$2:$K$7</definedName>
+    <definedName name="List_ProcessingStage">'Users'!$L$2:$L$5</definedName>
+    <definedName name="List_AckSent">'Users'!$M$2:$M$3</definedName>
+    <definedName name="List_AIPriority">'Users'!$N$2:$N$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -131,12 +134,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -150,6 +149,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FECACA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FDE68A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -178,13 +184,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FCA5A5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FDE68A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -304,12 +303,12 @@
           </spPr>
           <cat>
             <strRef>
-              <f>'Dashboard'!$D$4:$D$8</f>
+              <f>'Dashboard'!$D$4:$D$9</f>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$4:$E$8</f>
+              <f>'Dashboard'!$E$4:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -413,7 +412,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2880000"/>
@@ -435,7 +434,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2880000"/>
@@ -457,9 +456,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ITTickets" displayName="ITTickets" ref="A1:AA4" headerRowCount="1">
-  <autoFilter ref="A1:AA4"/>
-  <tableColumns count="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ITTickets" displayName="ITTickets" ref="A1:AF4" headerRowCount="1">
+  <autoFilter ref="A1:AF4"/>
+  <tableColumns count="32">
     <tableColumn id="1" name="Ticket ID"/>
     <tableColumn id="2" name="Created Date"/>
     <tableColumn id="3" name="Created Time"/>
@@ -485,8 +484,13 @@
     <tableColumn id="23" name="Escalation Level"/>
     <tableColumn id="24" name="Resolution"/>
     <tableColumn id="25" name="Closure Reason"/>
-    <tableColumn id="26" name="Ticket Age Days"/>
-    <tableColumn id="27" name="SLA Remaining Hours"/>
+    <tableColumn id="26" name="Processing Stage"/>
+    <tableColumn id="27" name="Ack Sent"/>
+    <tableColumn id="28" name="AI Issue Summary"/>
+    <tableColumn id="29" name="AI Priority"/>
+    <tableColumn id="30" name="AI Scope"/>
+    <tableColumn id="31" name="Ticket Age Days"/>
+    <tableColumn id="32" name="SLA Remaining Hours"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -796,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -959,57 +963,76 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF(Tickets!$L$2:$L$5000,"Closed")</f>
+        <f>COUNTIF(Tickets!$L$2:$L$5000,"Needs Review")</f>
         <v/>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Needs Review</t>
         </is>
       </c>
       <c r="E8" s="4">
-        <f>COUNTIF(Tickets!$L$2:$L$5000,"Closed")</f>
+        <f>COUNTIF(Tickets!$L$2:$L$5000,"Needs Review")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>High Priority Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIFS(Tickets!$I$2:$I$5000,"High",Tickets!$L$2:$L$5000,"&lt;&gt;Closed")</f>
+        <f>COUNTIF(Tickets!$L$2:$L$5000,"Closed")</f>
+        <v/>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" s="4">
+        <f>COUNTIF(Tickets!$L$2:$L$5000,"Closed")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>High Priority Open</t>
         </is>
       </c>
       <c r="B10" s="5">
-        <f>COUNTIF(Tickets!$M$2:$M$5000,"Unassigned")</f>
+        <f>COUNTIFS(Tickets!$I$2:$I$5000,"High",Tickets!$L$2:$L$5000,"&lt;&gt;Closed")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>COUNTIF(Tickets!$M$2:$M$5000,"Unassigned")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>Avg Age (Open Days)</t>
         </is>
       </c>
-      <c r="B11" s="5">
-        <f>IFERROR(AVERAGEIF(Tickets!$L$2:$L$5000,"&lt;&gt;Closed",Tickets!$Z$2:$Z$5000),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="B12" s="5">
+        <f>IFERROR(AVERAGEIF(Tickets!$L$2:$L$5000,"&lt;&gt;Closed",Tickets!$AE$2:$AE$5000),0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
@@ -1021,40 +1044,30 @@
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Engineer Workload (non-closed)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Open Tickets</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Unassigned</t>
-        </is>
-      </c>
-      <c r="B26" s="4">
-        <f>COUNTIFS(Tickets!$M$2:$M$5000,A26,Tickets!$L$2:$L$5000,"&lt;&gt;Closed")</f>
-        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Rushak Pachpande</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="B27" s="4">
@@ -1065,7 +1078,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>IT Engineer 1</t>
+          <t>Rushak Pachpande</t>
         </is>
       </c>
       <c r="B28" s="4">
@@ -1076,11 +1089,22 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>IT Engineer 2</t>
+          <t>IT Engineer 1</t>
         </is>
       </c>
       <c r="B29" s="4">
         <f>COUNTIFS(Tickets!$M$2:$M$5000,A29,Tickets!$L$2:$L$5000,"&lt;&gt;Closed")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>IT Engineer 2</t>
+        </is>
+      </c>
+      <c r="B30" s="4">
+        <f>COUNTIFS(Tickets!$M$2:$M$5000,A30,Tickets!$L$2:$L$5000,"&lt;&gt;Closed")</f>
         <v/>
       </c>
     </row>
@@ -1099,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1119,7 +1143,7 @@
     <col width="35" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
@@ -1127,8 +1151,13 @@
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="42" customWidth="1" min="26" max="26"/>
-    <col width="42" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
+    <col width="42" customWidth="1" min="31" max="31"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1259,10 +1288,35 @@
       </c>
       <c r="Z1" s="2" t="inlineStr">
         <is>
+          <t>Processing Stage</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>Ack Sent</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>AI Issue Summary</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>AI Priority</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>AI Scope</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
           <t>Ticket Age Days</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>SLA Remaining Hours</t>
         </is>
@@ -1275,7 +1329,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
@@ -1350,11 +1404,11 @@
       </c>
       <c r="R2" s="7" t="inlineStr">
         <is>
-          <t>Processed/Open Tickets</t>
+          <t>Open Tickets</t>
         </is>
       </c>
       <c r="S2" s="8" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="T2" s="7" t="n"/>
       <c r="U2" s="9" t="inlineStr"/>
@@ -1370,12 +1424,37 @@
       </c>
       <c r="X2" s="7" t="inlineStr"/>
       <c r="Y2" s="7" t="inlineStr"/>
-      <c r="Z2" s="10">
+      <c r="Z2" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AA2" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" s="9" t="inlineStr">
+        <is>
+          <t>VPN connection fails with error 809 after a Windows update.</t>
+        </is>
+      </c>
+      <c r="AC2" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD2" s="9" t="inlineStr">
+        <is>
+          <t>VPN client / Engineering user Priya Sharma</t>
+        </is>
+      </c>
+      <c r="AE2" s="10">
         <f>IF(A2="","",IF(L2="Closed",IF(T2="",0,MAX(0,T2-B2)),MAX(0,TODAY()-B2)))</f>
         <v/>
       </c>
-      <c r="AA2" s="11">
-        <f>IF(OR(A2="",L2="Closed"),"",IF(I2="High",SLA_High,IF(I2="Low",SLA_Low,SLA_Medium))-Z2*24)</f>
+      <c r="AF2" s="11">
+        <f>IF(OR(A2="",L2="Closed"),"",IF(I2="High",SLA_High,IF(I2="Low",SLA_Low,SLA_Medium))-AE2*24)</f>
         <v/>
       </c>
     </row>
@@ -1386,7 +1465,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
@@ -1457,11 +1536,11 @@
       </c>
       <c r="R3" s="7" t="inlineStr">
         <is>
-          <t>Processed/Open Tickets</t>
+          <t>Open Tickets</t>
         </is>
       </c>
       <c r="S3" s="8" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="T3" s="7" t="n"/>
       <c r="U3" s="9" t="inlineStr"/>
@@ -1477,12 +1556,37 @@
       </c>
       <c r="X3" s="7" t="inlineStr"/>
       <c r="Y3" s="7" t="inlineStr"/>
-      <c r="Z3" s="10">
+      <c r="Z3" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AA3" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" s="9" t="inlineStr">
+        <is>
+          <t>Outlook search returns no results for recent mail.</t>
+        </is>
+      </c>
+      <c r="AC3" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="9" t="inlineStr">
+        <is>
+          <t>Outlook / Sales user Amit Patel</t>
+        </is>
+      </c>
+      <c r="AE3" s="10">
         <f>IF(A3="","",IF(L3="Closed",IF(T3="",0,MAX(0,T3-B3)),MAX(0,TODAY()-B3)))</f>
         <v/>
       </c>
-      <c r="AA3" s="11">
-        <f>IF(OR(A3="",L3="Closed"),"",IF(I3="High",SLA_High,IF(I3="Low",SLA_Low,SLA_Medium))-Z3*24)</f>
+      <c r="AF3" s="11">
+        <f>IF(OR(A3="",L3="Closed"),"",IF(I3="High",SLA_High,IF(I3="Low",SLA_Low,SLA_Medium))-AE3*24)</f>
         <v/>
       </c>
     </row>
@@ -1493,7 +1597,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
@@ -1568,14 +1672,14 @@
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>Processed/Closed</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="S4" s="8" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
@@ -1598,12 +1702,37 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="Z4" s="10">
+      <c r="Z4" s="7" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AA4" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Windows 11 laptop setup for a new joiner.</t>
+        </is>
+      </c>
+      <c r="AC4" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD4" s="9" t="inlineStr">
+        <is>
+          <t>Laptop / HR new joiner</t>
+        </is>
+      </c>
+      <c r="AE4" s="10">
         <f>IF(A4="","",IF(L4="Closed",IF(T4="",0,MAX(0,T4-B4)),MAX(0,TODAY()-B4)))</f>
         <v/>
       </c>
-      <c r="AA4" s="11">
-        <f>IF(OR(A4="",L4="Closed"),"",IF(I4="High",SLA_High,IF(I4="Low",SLA_Low,SLA_Medium))-Z4*24)</f>
+      <c r="AF4" s="11">
+        <f>IF(OR(A4="",L4="Closed"),"",IF(I4="High",SLA_High,IF(I4="Low",SLA_Low,SLA_Medium))-AE4*24)</f>
         <v/>
       </c>
     </row>
@@ -1616,31 +1745,34 @@
       <formula>"New"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"Needs Review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"Pending"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
       <formula>"Closed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I5000">
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="5">
       <formula>"High"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M5000">
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
       <formula>"Unassigned"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA5000">
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="6">
+  <conditionalFormatting sqref="AF2:AF5000">
+    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="6">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="11">
     <dataValidation sqref="I2:I5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>=List_Priority</formula1>
     </dataValidation>
@@ -1665,6 +1797,15 @@
     <dataValidation sqref="Y2:Y5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
       <formula1>=List_ClosureReason</formula1>
     </dataValidation>
+    <dataValidation sqref="Z2:Z5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
+      <formula1>=List_ProcessingStage</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA2:AA5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
+      <formula1>=List_AckSent</formula1>
+    </dataValidation>
+    <dataValidation sqref="AC2:AC5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Please select a value from the dropdown list." type="list">
+      <formula1>=List_AIPriority</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -1814,7 +1955,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1967,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31 17:40:25</t>
+          <t>2026-08-01 01:10:46</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1982,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Upload this workbook to OneDrive/SharePoint under the IT Support account. In n8n Excel nodes, reselect this workbook and the ITTickets / AuditLog tables after upload (workbook and table IDs are tenant-specific). CreatedDate / ClosedDate are real Excel dates (display dd-mm-yyyy).</t>
+          <t>Upload this workbook to OneDrive/SharePoint under the IT Support account. In n8n Excel nodes, reselect this workbook and the ITTickets / AuditLog tables after upload (workbook and table IDs are tenant-specific). CreatedDate / ClosedDate are real Excel dates (display dd-mm-yyyy). Processing Stage / Ack Sent enable fault-tolerant resume; AI columns hold LLM summaries. Outlook folders: Inbox, Open Tickets, Processed.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1950,12 +2091,15 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2009,6 +2153,21 @@
           <t>ClosureReasonList</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ProcessingStageList</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>AckSentList</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>AIPriorityList</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -2061,6 +2220,21 @@
           <t>Completed</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2113,6 +2287,21 @@
           <t>Cancelled by User</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Acked</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2165,6 +2354,16 @@
           <t>Duplicate Ticket</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2208,30 +2407,45 @@
           <t>No Response from User</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NeedsReview</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="F6" t="inlineStr">
         <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Resolved - Access Granted</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Out of Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Resolved - Access Granted</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Out of Scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
       <c r="H7" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -2336,7 +2550,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31 17:40:25</t>
+          <t>2026-08-01 01:10:46</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
